--- a/宣汉县人民医院医共体联合办公室自有资产清单.xlsx
+++ b/宣汉县人民医院医共体联合办公室自有资产清单.xlsx
@@ -90,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -110,6 +110,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -527,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -609,7 +613,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>8根</t>
+          <t>4根</t>
         </is>
       </c>
     </row>
@@ -669,7 +673,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>14根</t>
+          <t>13根</t>
         </is>
       </c>
     </row>
@@ -745,8 +749,50 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>打印机</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>1台</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>A4打印纸</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>2包</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>签字确认人员：徐浩航  王丹  李俊秀</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n"/>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>日　　期：2026年10月21日</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
